--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121275997</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121275973</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275997</v>
+        <v>121275973</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -708,25 +708,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitteberg, Dls</t>
+          <t>Lintjärnen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>314668</v>
+        <v>314877</v>
       </c>
       <c r="R2" t="n">
-        <v>6523394</v>
+        <v>6523438</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275973</v>
+        <v>121275997</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -823,21 +819,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dls</t>
+          <t>Vitteberg, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>314877</v>
+        <v>314668</v>
       </c>
       <c r="R3" t="n">
-        <v>6523438</v>
+        <v>6523394</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275973</v>
+        <v>121275997</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,21 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dls</t>
+          <t>Vitteberg, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>314877</v>
+        <v>314668</v>
       </c>
       <c r="R2" t="n">
-        <v>6523438</v>
+        <v>6523394</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275997</v>
+        <v>121275973</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +823,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vitteberg, Dls</t>
+          <t>Lintjärnen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>314668</v>
+        <v>314877</v>
       </c>
       <c r="R3" t="n">
-        <v>6523394</v>
+        <v>6523438</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275997</v>
+        <v>121275973</v>
       </c>
       <c r="B2" t="n">
         <v>57354</v>
@@ -708,25 +708,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitteberg, Dls</t>
+          <t>Lintjärnen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>314668</v>
+        <v>314877</v>
       </c>
       <c r="R2" t="n">
-        <v>6523394</v>
+        <v>6523438</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275973</v>
+        <v>121275997</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -823,21 +819,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dls</t>
+          <t>Vitteberg, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>314877</v>
+        <v>314668</v>
       </c>
       <c r="R3" t="n">
-        <v>6523438</v>
+        <v>6523394</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275973</v>
+        <v>121275997</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,21 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dls</t>
+          <t>Vitteberg, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>314877</v>
+        <v>314668</v>
       </c>
       <c r="R2" t="n">
-        <v>6523438</v>
+        <v>6523394</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275997</v>
+        <v>121275973</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +823,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vitteberg, Dls</t>
+          <t>Lintjärnen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>314668</v>
+        <v>314877</v>
       </c>
       <c r="R3" t="n">
-        <v>6523394</v>
+        <v>6523438</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121275997</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121275973</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275997</v>
+        <v>121275973</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -708,25 +708,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitteberg, Dls</t>
+          <t>Lintjärnen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>314668</v>
+        <v>314877</v>
       </c>
       <c r="R2" t="n">
-        <v>6523394</v>
+        <v>6523438</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275973</v>
+        <v>121275997</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -823,21 +819,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dls</t>
+          <t>Vitteberg, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>314877</v>
+        <v>314668</v>
       </c>
       <c r="R3" t="n">
-        <v>6523438</v>
+        <v>6523394</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121275973</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,12 +784,7 @@
         <v>121275997</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47656-2024 artfynd.xlsx
+++ b/artfynd/A 47656-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275973</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275997</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>